--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -1065,7 +1065,7 @@
         <v>117703871</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>57511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>80344183</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>82262985</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,6 +1184,234 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123697326</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58186</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr Lindberg Berga,Leksand, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>507031</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6741817</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders J. Dahlin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders J. Dahlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123697316</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr Lindberg Berga,Leksand, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>507031</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6741817</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders J. Dahlin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders J. Dahlin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -1186,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123697326</v>
+        <v>123697316</v>
       </c>
       <c r="B6" t="n">
-        <v>58186</v>
+        <v>57437</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,30 +1198,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123697316</v>
+        <v>123697326</v>
       </c>
       <c r="B7" t="n">
-        <v>57431</v>
+        <v>58192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -1189,7 +1189,7 @@
         <v>123697316</v>
       </c>
       <c r="B6" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>123697326</v>
       </c>
       <c r="B7" t="n">
-        <v>58192</v>
+        <v>58195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -1186,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123697316</v>
+        <v>123697326</v>
       </c>
       <c r="B6" t="n">
-        <v>57440</v>
+        <v>58196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,30 +1198,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123697326</v>
+        <v>123697316</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>57441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -1186,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123697326</v>
+        <v>123697316</v>
       </c>
       <c r="B6" t="n">
-        <v>58196</v>
+        <v>57441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,30 +1198,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123697316</v>
+        <v>123697326</v>
       </c>
       <c r="B7" t="n">
-        <v>57441</v>
+        <v>58196</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 66933-2021 artfynd.xlsx
+++ b/artfynd/A 66933-2021 artfynd.xlsx
@@ -1186,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123697316</v>
+        <v>123697326</v>
       </c>
       <c r="B6" t="n">
-        <v>57441</v>
+        <v>58196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,30 +1198,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123697326</v>
+        <v>123697316</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>57441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
